--- a/data/trans_orig/IP31KM04_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM04_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28259</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>21988</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>34576</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>52,61%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>64,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>26891</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>17578</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35163</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>50,08%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,73%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>65,48%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>30545</t>
+          <t>25795</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23324</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37070</t>
+          <t>31416</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>56,19%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>44,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>57435</t>
+          <t>54054</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45678</t>
+          <t>45258</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68465</t>
+          <t>63072</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>40,77%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>63,31%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>25456</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>19139</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31727</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>47,39%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>59,07%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>26808</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>18536</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>36121</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>49,92%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>34,52%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>67,27%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>27800</t>
+          <t>20110</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>35021</t>
+          <t>25685</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>54608</t>
+          <t>45566</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43578</t>
+          <t>36548</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>66365</t>
+          <t>54362</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>45,74%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>59,23%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>53699</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58345</t>
+          <t>45905</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>99620</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>212354</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>193168</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>235675</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>45,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>41,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>50,53%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>184339</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>149140</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>204068</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>40,8%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>33,01%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>45,16%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>285</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>231773</t>
+          <t>183195</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>206447</t>
+          <t>165853</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>256924</t>
+          <t>200936</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,85%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>416112</t>
+          <t>395550</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>373606</t>
+          <t>366277</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>452662</t>
+          <t>422692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>43,48%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,04%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,3%</t>
+          <t>47,44%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>254069</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>230748</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>273255</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>54,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>49,47%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>58,59%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>355</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>267493</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>247764</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>302692</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>59,2%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>54,84%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>66,99%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>345</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>273477</t>
+          <t>241471</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>248326</t>
+          <t>223730</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>298803</t>
+          <t>258813</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>54,13%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,15%</t>
+          <t>52,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>540970</t>
+          <t>495540</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>504420</t>
+          <t>468398</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>583476</t>
+          <t>524813</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>56,52%</t>
+          <t>55,61%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,7%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>60,96%</t>
+          <t>58,9%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>466423</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>625</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>451832</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>630</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>505250</t>
+          <t>424666</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>957082</t>
+          <t>891090</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>79686</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67533</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>90154</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>47,81%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>40,51%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>54,09%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>102</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>65417</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>55764</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>74906</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>44,75%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>38,15%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>51,24%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>84196</t>
+          <t>67103</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>71810</t>
+          <t>56840</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>97725</t>
+          <t>77137</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>45,61%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,95%</t>
+          <t>52,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>149613</t>
+          <t>146788</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134185</t>
+          <t>131860</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>166008</t>
+          <t>162397</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>50,72%</t>
+          <t>51,75%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>76532</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>99153</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>52,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>45,91%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>59,49%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>80769</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>71280</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>90422</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>55,25%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>48,76%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>61,85%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>96943</t>
+          <t>80037</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>83414</t>
+          <t>70003</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109329</t>
+          <t>90300</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,05%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>61,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>177711</t>
+          <t>167037</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161316</t>
+          <t>151428</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>193139</t>
+          <t>181965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>49,28%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>57,98%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181139</t>
+          <t>147140</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>437</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>320299</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>298651</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>346673</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>46,63%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>43,48%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>50,47%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>407</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>276647</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>238232</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>303764</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>42,45%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>46,61%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>437</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>346514</t>
+          <t>276094</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>316080</t>
+          <t>254982</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>374094</t>
+          <t>297048</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,44%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>50,23%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>623161</t>
+          <t>596392</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>577764</t>
+          <t>564104</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>663302</t>
+          <t>631341</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>43,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>48,4%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>366525</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>340151</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>388173</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>53,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>49,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>56,52%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>507</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>375070</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>347953</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>413485</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>57,55%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>53,39%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,45%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>503</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>398219</t>
+          <t>341617</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>370639</t>
+          <t>320663</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>428653</t>
+          <t>362729</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>55,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>773289</t>
+          <t>708143</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>733148</t>
+          <t>673194</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>818686</t>
+          <t>740431</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>54,28%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>51,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>56,76%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>914</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>651717</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>617711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1396450</t>
+          <t>1304535</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
